--- a/Assignment 2/robodk_stations-master/points_2026.xlsx
+++ b/Assignment 2/robodk_stations-master/points_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mtrkd\Documents\GitHub\ENMT482-Robot-Coffee-Special\Assignment 2\robodk_stations-master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0ED8E31C-13B7-491B-8131-6D0C79A986ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C959B75-33FB-48D4-8C52-5231D36C8EFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{E8225CB9-45CE-4437-8AC0-83402CB2D7CC}"/>
+    <workbookView xWindow="5820" yWindow="0" windowWidth="21600" windowHeight="15600" xr2:uid="{E8225CB9-45CE-4437-8AC0-83402CB2D7CC}"/>
   </bookViews>
   <sheets>
     <sheet name="robot_3" sheetId="6" r:id="rId1"/>
